--- a/Student_Performance_Analysis.xlsx
+++ b/Student_Performance_Analysis.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83787009-7112-4AA7-A337-AF0D2F6BE217}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB023E1-7E8D-432F-9ABC-095C759BBEF7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{5011460C-5197-4BD2-8072-85EBD7DB5981}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="3" xr2:uid="{5011460C-5197-4BD2-8072-85EBD7DB5981}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
+    <sheet name="Pivot_Tables" sheetId="3" r:id="rId1"/>
     <sheet name="Raw_Data" sheetId="1" r:id="rId2"/>
     <sheet name="Analysis" sheetId="2" r:id="rId3"/>
+    <sheet name="Dashboard" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="44">
   <si>
     <t>Student Name</t>
   </si>
@@ -298,7 +299,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Student_Performance_Analysis.xlsx]Sheet2!PivotTable1</c:name>
+    <c:name>[Student_Performance_Analysis.xlsx]Pivot_Tables!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -403,7 +404,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$B$3</c:f>
+              <c:f>Pivot_Tables!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -482,7 +483,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet2!$A$4:$A$30</c:f>
+              <c:f>Pivot_Tables!$A$4:$A$30</c:f>
               <c:strCache>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
@@ -568,7 +569,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$B$4:$B$30</c:f>
+              <c:f>Pivot_Tables!$B$4:$B$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
@@ -879,6 +880,1107 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Student_Performance_Analysis.xlsx]Pivot_Tables!PivotTable1</c:name>
+    <c:fmtId val="2"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pivot_Tables!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pivot_Tables!$A$4:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>Aravind</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Bhavani</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chandra</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Divya</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Eesha</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Fathima</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Gopi</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Harish</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Indira</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Janaki</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Karthik</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Lakshmi</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Madhu</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Nalini</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Oviya</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Praveen</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Queen</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Ramya</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Sathish</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Thiru</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Uma</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Varun</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Wazir</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Xavier</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Yasmin</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Zeel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pivot_Tables!$B$4:$B$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>499</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>278</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>339</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>264</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>316</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>286</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>269</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>221</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>138</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BA5E-49A0-8C6D-B5A93123757C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1359784016"/>
+        <c:axId val="1355707760"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1359784016"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1355707760"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1355707760"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1359784016"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Subject Average Comparison</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$A$3:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Total Students  </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Average Total Marks</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Highest Total Marks </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Lowest Total Marks</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Average Maths</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Average English</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Average Science</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Average Social Science</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$B$3:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>47.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54.84</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50.35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>48.61</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>54.72</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EF2F-4BA9-AFCB-EC7235D0996E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1615036016"/>
+        <c:axId val="1610817664"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1615036016"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1610817664"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1610817664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1615036016"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -919,7 +2021,1093 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1455,6 +3643,85 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Student Total Marks Comparison">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2EE145F-9BFF-43C1-990A-371D12634C3C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>487680</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57BD81A7-8DED-42EE-A035-6FC7B1C56E5C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2329,7 +4596,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5E3ED281-8F4B-46B4-B1D3-9AAC78C0A9FE}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5E3ED281-8F4B-46B4-B1D3-9AAC78C0A9FE}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0">
@@ -2461,8 +4728,17 @@
   <dataFields count="1">
     <dataField name="Total marks" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5141,4 +7417,99 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFAC0195-3ABF-4926-ABF3-50ABA5D3774C}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+    </row>
+    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="6">
+        <f>COUNTA(Raw_Data!A2:A101)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="6">
+        <f>AVERAGE(Raw_Data!F2:F101)</f>
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="6">
+        <f>MAX(Raw_Data!F2:F101)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="6">
+        <f>MIN(Raw_Data!F2:F101)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="6">
+        <f>AVERAGE(Raw_Data!B2:B101)</f>
+        <v>54.84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6">
+        <f>AVERAGE(Raw_Data!C2:C101)</f>
+        <v>50.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6">
+        <f>AVERAGE(Raw_Data!D2:D101)</f>
+        <v>48.61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6">
+        <f>AVERAGE(Raw_Data!E2:E101)</f>
+        <v>54.72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>